--- a/მომსახურების ანაზღაურება დელ.xlsx
+++ b/მომსახურების ანაზღაურება დელ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nana\bank-summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4068CC87-E251-43C9-8239-505C8A9CEBBC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B1FE455-AE1D-41D1-B99B-04936F2CB248}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="გადასატანი" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="108">
   <si>
     <t>8</t>
   </si>
@@ -408,7 +408,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -424,6 +424,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
@@ -456,7 +462,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -490,6 +496,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -805,27 +814,27 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>32</v>
+      <c r="A2">
+        <v>47001040600</v>
       </c>
       <c r="B2" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A2,ინფო!A:A,0))</f>
-        <v>დავითი</v>
+        <v>რობერტ</v>
       </c>
       <c r="C2" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A2,ინფო!A:A,0))</f>
-        <v>საყვარელიძე</v>
+        <v>ელოიძე</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>0</v>
       </c>
       <c r="E2">
         <f>INDEX(თანხები!D:D,MATCH(A2,თანხები!A:A,0))</f>
-        <v>6850.67</v>
+        <v>3994.25</v>
       </c>
       <c r="F2" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A2,ინფო!A:A,0))</f>
-        <v>თბილისი გუდამაყრის ქ. N 2 ბ. 102</v>
+        <v>თბილისი</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>1</v>
@@ -833,49 +842,49 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="B3" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A3,ინფო!A:A,0))</f>
-        <v>საბა</v>
+        <v>გიორგი</v>
       </c>
       <c r="C3" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A3,ინფო!A:A,0))</f>
-        <v>ცაგარეიშვილი</v>
+        <v>მელაძე</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>0</v>
       </c>
       <c r="E3">
         <f>INDEX(თანხები!D:D,MATCH(A3,თანხები!A:A,0))</f>
-        <v>6123.55</v>
+        <v>5656.84</v>
       </c>
       <c r="F3" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A3,ინფო!A:A,0))</f>
-        <v>თბილისი</v>
+        <v>საქართველო, ქალაქი თბილისი, ნიკოლოზ ანთელავას ქუჩა, N 4(ყოფ. პ. იბერის ქ.)</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4">
-        <v>47001040600</v>
+      <c r="A4" t="s">
+        <v>74</v>
       </c>
       <c r="B4" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A4,ინფო!A:A,0))</f>
-        <v>რობერტ</v>
+        <v>გიორგი</v>
       </c>
       <c r="C4" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A4,ინფო!A:A,0))</f>
-        <v>ელოიძე</v>
+        <v>მეტრეველი</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>0</v>
       </c>
       <c r="E4">
         <f>INDEX(თანხები!D:D,MATCH(A4,თანხები!A:A,0))</f>
-        <v>5267.37</v>
+        <v>4045.36</v>
       </c>
       <c r="F4" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A4,ინფო!A:A,0))</f>
@@ -887,26 +896,26 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="B5" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A5,ინფო!A:A,0))</f>
-        <v>ნინო</v>
+        <v>დავითი</v>
       </c>
       <c r="C5" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A5,ინფო!A:A,0))</f>
-        <v>კვარაცხელია</v>
+        <v>საყვარელიძე</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>0</v>
       </c>
       <c r="E5">
         <f>INDEX(თანხები!D:D,MATCH(A5,თანხები!A:A,0))</f>
-        <v>4306.4799999999996</v>
+        <v>3089.22</v>
       </c>
       <c r="F5" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A5,ინფო!A:A,0))</f>
-        <v>საქართველო, ქალაქი თბილისი, ფიროსმანის ქუჩა, N 3</v>
+        <v>თბილისი გუდამაყრის ქ. N 2 ბ. 102</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>1</v>
@@ -914,26 +923,26 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="B6" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A6,ინფო!A:A,0))</f>
-        <v>გიორგი</v>
+        <v>საბა</v>
       </c>
       <c r="C6" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A6,ინფო!A:A,0))</f>
-        <v>მელაძე</v>
+        <v>ცაგარეიშვილი</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>0</v>
       </c>
       <c r="E6">
         <f>INDEX(თანხები!D:D,MATCH(A6,თანხები!A:A,0))</f>
-        <v>4267.5200000000004</v>
+        <v>6938.23</v>
       </c>
       <c r="F6" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A6,ინფო!A:A,0))</f>
-        <v>საქართველო, ქალაქი თბილისი, ნიკოლოზ ანთელავას ქუჩა, N 4(ყოფ. პ. იბერის ქ.)</v>
+        <v>თბილისი</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>1</v>
@@ -941,26 +950,26 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B7" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A7,ინფო!A:A,0))</f>
-        <v>გიორგი</v>
+        <v>ნინო</v>
       </c>
       <c r="C7" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A7,ინფო!A:A,0))</f>
-        <v>მეტრეველი</v>
+        <v>კვარაცხელია</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>0</v>
       </c>
       <c r="E7">
         <f>INDEX(თანხები!D:D,MATCH(A7,თანხები!A:A,0))</f>
-        <v>4185.6099999999997</v>
+        <v>1542.97</v>
       </c>
       <c r="F7" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A7,ინფო!A:A,0))</f>
-        <v>თბილისი</v>
+        <v>საქართველო, ქალაქი თბილისი, ფიროსმანის ქუჩა, N 3</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>1</v>
@@ -968,26 +977,26 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="B8" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A8,ინფო!A:A,0))</f>
-        <v>ბადრი</v>
+        <v>საბა</v>
       </c>
       <c r="C8" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A8,ინფო!A:A,0))</f>
-        <v>სირაძე</v>
+        <v>კუპატაძე</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>0</v>
       </c>
       <c r="E8">
         <f>INDEX(თანხები!D:D,MATCH(A8,თანხები!A:A,0))</f>
-        <v>3712.89</v>
+        <v>4137.97</v>
       </c>
       <c r="F8" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A8,ინფო!A:A,0))</f>
-        <v>თბილისი გარდაბნის გზატ. N 42</v>
+        <v>თბილისი</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>1</v>
@@ -995,26 +1004,26 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="B9" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A9,ინფო!A:A,0))</f>
-        <v>ოთარ</v>
+        <v>ბადრი</v>
       </c>
       <c r="C9" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A9,ინფო!A:A,0))</f>
-        <v>კუპრეიშვილი</v>
+        <v>სირაძე</v>
       </c>
       <c r="D9" s="8">
         <v>8</v>
       </c>
       <c r="E9">
         <f>INDEX(თანხები!D:D,MATCH(A9,თანხები!A:A,0))</f>
-        <v>3305.06</v>
+        <v>2589.4899999999998</v>
       </c>
       <c r="F9" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A9,ინფო!A:A,0))</f>
-        <v>საქართველო, ქალაქი ფოთი, უშანგი ჩხეიძის ქუჩა, N 3, ბინა 11</v>
+        <v>თბილისი გარდაბნის გზატ. N 42</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>1</v>
@@ -1022,53 +1031,53 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="B10" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A10,ინფო!A:A,0))</f>
-        <v>მიხეილ</v>
+        <v>ლუკას</v>
       </c>
       <c r="C10" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A10,ინფო!A:A,0))</f>
-        <v>ლომჯარია</v>
+        <v>ელიშაკოვი</v>
       </c>
       <c r="D10" s="8">
         <v>8</v>
       </c>
       <c r="E10">
         <f>INDEX(თანხები!D:D,MATCH(A10,თანხები!A:A,0))</f>
-        <v>2962.01</v>
+        <v>926.33</v>
       </c>
       <c r="F10" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A10,ინფო!A:A,0))</f>
-        <v>საქართველო, ქალაქი თბილისი, შალვა ნუცუბიძის ფერდობი, IV მიკრო/რაიონი, კორპუსი 12, ბინა 3</v>
+        <v>თბილისი</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11">
-        <v>62003016407</v>
+      <c r="A11" t="s">
+        <v>5</v>
       </c>
       <c r="B11" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A11,ინფო!A:A,0))</f>
-        <v>დავით</v>
+        <v>მიხეილ</v>
       </c>
       <c r="C11" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A11,ინფო!A:A,0))</f>
-        <v>სვირავა</v>
+        <v>ლომჯარია</v>
       </c>
       <c r="D11" s="8">
         <v>8</v>
       </c>
       <c r="E11">
         <f>INDEX(თანხები!D:D,MATCH(A11,თანხები!A:A,0))</f>
-        <v>992.53</v>
+        <v>2244.14</v>
       </c>
       <c r="F11" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A11,ინფო!A:A,0))</f>
-        <v>თბილისი</v>
+        <v>საქართველო, ქალაქი თბილისი, შალვა ნუცუბიძის ფერდობი, IV მიკრო/რაიონი, კორპუსი 12, ბინა 3</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>1</v>
@@ -1076,53 +1085,50 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="B12" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A12,ინფო!A:A,0))</f>
-        <v>ლუკას</v>
+        <v>ოთარ</v>
       </c>
       <c r="C12" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A12,ინფო!A:A,0))</f>
-        <v>ელიშაკოვი</v>
+        <v>კუპრეიშვილი</v>
       </c>
       <c r="D12" s="8">
         <v>8</v>
       </c>
       <c r="E12">
         <f>INDEX(თანხები!D:D,MATCH(A12,თანხები!A:A,0))</f>
-        <v>970.3</v>
+        <v>34.270000000000003</v>
       </c>
       <c r="F12" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A12,ინფო!A:A,0))</f>
-        <v>თბილისი</v>
+        <v>საქართველო, ქალაქი ფოთი, უშანგი ჩხეიძის ქუჩა, N 3, ბინა 11</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" t="s">
-        <v>107</v>
-      </c>
-      <c r="B13" s="8" t="str">
+      <c r="B13" s="8" t="e">
         <f>INDEX(ინფო!B:B,MATCH(A13,ინფო!A:A,0))</f>
-        <v>საბა</v>
-      </c>
-      <c r="C13" s="8" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="C13" s="8" t="e">
         <f>INDEX(ინფო!C:C,MATCH(A13,ინფო!A:A,0))</f>
-        <v>კუპატაძე</v>
+        <v>#N/A</v>
       </c>
       <c r="D13" s="8">
         <v>8</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="e">
         <f>INDEX(თანხები!D:D,MATCH(A13,თანხები!A:A,0))</f>
-        <v>560.46</v>
-      </c>
-      <c r="F13" s="5" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="F13" s="5" t="e">
         <f>INDEX(ინფო!D:D,MATCH(A13,ინფო!A:A,0))</f>
-        <v>თბილისი</v>
+        <v>#N/A</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>1</v>
@@ -1698,103 +1704,104 @@
     <row r="2" spans="1:5">
       <c r="A2" t="str">
         <f>INDEX(ინფო!A:A,MATCH(C2,ინფო!C:C,0))</f>
-        <v>38001048993</v>
+        <v>01001083359</v>
       </c>
       <c r="B2" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C2,ინფო!C:C,0))</f>
-        <v>დავითი</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="19">
-        <v>6850.67</v>
-      </c>
-      <c r="E2" s="5"/>
+        <v>საბა</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" s="18">
+        <v>6938.23</v>
+      </c>
+      <c r="E2" s="22"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="str">
         <f>INDEX(ინფო!A:A,MATCH(C3,ინფო!C:C,0))</f>
-        <v>01001083359</v>
+        <v>01030053229</v>
       </c>
       <c r="B3" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C3,ინფო!C:C,0))</f>
-        <v>საბა</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="19">
-        <v>6123.55</v>
-      </c>
-      <c r="E3" s="5"/>
+        <v>გიორგი</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="18">
+        <v>5656.84</v>
+      </c>
+      <c r="E3" s="22"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4">
+      <c r="A4" t="str">
         <f>INDEX(ინფო!A:A,MATCH(C4,ინფო!C:C,0))</f>
-        <v>47001040600</v>
+        <v>01027090847</v>
       </c>
       <c r="B4" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C4,ინფო!C:C,0))</f>
-        <v>რობერტ</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="D4" s="19">
-        <v>5267.37</v>
-      </c>
-      <c r="E4" s="5"/>
+        <v>საბა</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="18">
+        <v>4137.97</v>
+      </c>
+      <c r="E4" s="22"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="str">
         <f>INDEX(ინფო!A:A,MATCH(C5,ინფო!C:C,0))</f>
-        <v>01030053301</v>
+        <v>01401103956</v>
       </c>
       <c r="B5" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C5,ინფო!C:C,0))</f>
-        <v>ნინო</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="19">
-        <v>4306.4799999999996</v>
-      </c>
-      <c r="E5" s="5"/>
+        <v>გიორგი</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="18">
+        <v>4045.36</v>
+      </c>
+      <c r="E5" s="22"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" t="str">
+      <c r="A6">
         <f>INDEX(ინფო!A:A,MATCH(C6,ინფო!C:C,0))</f>
-        <v>01030053229</v>
+        <v>47001040600</v>
       </c>
       <c r="B6" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C6,ინფო!C:C,0))</f>
-        <v>გიორგი</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="19">
-        <v>4267.5200000000004</v>
-      </c>
-      <c r="E6" s="5"/>
+        <v>რობერტ</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="18">
+        <v>3994.25</v>
+      </c>
+      <c r="E6" s="22"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="str">
         <f>INDEX(ინფო!A:A,MATCH(C7,ინფო!C:C,0))</f>
-        <v>01401103956</v>
+        <v>38001048993</v>
       </c>
       <c r="B7" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C7,ინფო!C:C,0))</f>
-        <v>გიორგი</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" s="19">
-        <v>4185.6099999999997</v>
-      </c>
+        <v>დავითი</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="18">
+        <v>3089.22</v>
+      </c>
+      <c r="E7" s="18"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="str">
@@ -1805,60 +1812,64 @@
         <f>INDEX(ინფო!B:B,MATCH(C8,ინფო!C:C,0))</f>
         <v>ბადრი</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="19">
-        <v>3712.89</v>
-      </c>
+      <c r="D8" s="18">
+        <v>2589.4899999999998</v>
+      </c>
+      <c r="E8" s="18"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="str">
         <f>INDEX(ინფო!A:A,MATCH(C9,ინფო!C:C,0))</f>
-        <v>42401042214</v>
+        <v>01010000461</v>
       </c>
       <c r="B9" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C9,ინფო!C:C,0))</f>
-        <v>ოთარ</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="19">
-        <v>3305.06</v>
-      </c>
+        <v>მიხეილ</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="18">
+        <v>2244.14</v>
+      </c>
+      <c r="E9" s="18"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="str">
         <f>INDEX(ინფო!A:A,MATCH(C10,ინფო!C:C,0))</f>
-        <v>01010000461</v>
+        <v>01401103956</v>
       </c>
       <c r="B10" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C10,ინფო!C:C,0))</f>
-        <v>მიხეილ</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="19">
-        <v>2962.01</v>
-      </c>
+        <v>გიორგი</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="18">
+        <v>2150</v>
+      </c>
+      <c r="E10" s="18"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11">
+      <c r="A11" t="str">
         <f>INDEX(ინფო!A:A,MATCH(C11,ინფო!C:C,0))</f>
-        <v>62003016407</v>
+        <v>01030053301</v>
       </c>
       <c r="B11" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C11,ინფო!C:C,0))</f>
-        <v>დავით</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="D11" s="19">
-        <v>992.53</v>
-      </c>
+        <v>ნინო</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="18">
+        <v>1542.97</v>
+      </c>
+      <c r="E11" s="18"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="str">
@@ -1869,38 +1880,47 @@
         <f>INDEX(ინფო!B:B,MATCH(C12,ინფო!C:C,0))</f>
         <v>ლუკას</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="D12" s="19">
-        <v>970.3</v>
-      </c>
+      <c r="D12" s="18">
+        <v>926.33</v>
+      </c>
+      <c r="E12" s="18"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="str">
         <f>INDEX(ინფო!A:A,MATCH(C13,ინფო!C:C,0))</f>
-        <v>01027090847</v>
+        <v>42401042214</v>
       </c>
       <c r="B13" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C13,ინფო!C:C,0))</f>
-        <v>საბა</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="D13" s="19">
-        <v>560.46</v>
-      </c>
+        <v>ოთარ</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="18">
+        <v>34.270000000000003</v>
+      </c>
+      <c r="E13" s="18"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" t="e">
+      <c r="A14">
         <f>INDEX(ინფო!A:A,MATCH(C14,ინფო!C:C,0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="B14" t="e">
+        <v>62003016407</v>
+      </c>
+      <c r="B14" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C14,ინფო!C:C,0))</f>
-        <v>#N/A</v>
-      </c>
+        <v>დავით</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="23">
+        <v>12.06</v>
+      </c>
+      <c r="E14" s="18"/>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="e">
@@ -1911,6 +1931,9 @@
         <f>INDEX(ინფო!B:B,MATCH(C15,ინფო!C:C,0))</f>
         <v>#N/A</v>
       </c>
+      <c r="C15" s="18"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="18"/>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="e">
@@ -1921,8 +1944,11 @@
         <f>INDEX(ინფო!B:B,MATCH(C16,ინფო!C:C,0))</f>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="17" spans="1:2">
+      <c r="C16" s="18"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="18"/>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="e">
         <f>INDEX(ინფო!A:A,MATCH(C17,ინფო!C:C,0))</f>
         <v>#N/A</v>
@@ -1931,8 +1957,11 @@
         <f>INDEX(ინფო!B:B,MATCH(C17,ინფო!C:C,0))</f>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="18" spans="1:2">
+      <c r="C17" s="18"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="18"/>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="e">
         <f>INDEX(ინფო!A:A,MATCH(C18,ინფო!C:C,0))</f>
         <v>#N/A</v>
@@ -1941,29 +1970,41 @@
         <f>INDEX(ინფო!B:B,MATCH(C18,ინფო!C:C,0))</f>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="19" spans="1:2">
+      <c r="C18" s="18"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="18"/>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19"/>
-    </row>
-    <row r="20" spans="1:2">
+      <c r="C19" s="18"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="18"/>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20"/>
-    </row>
-    <row r="21" spans="1:2">
+      <c r="C20" s="18"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="18"/>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21"/>
-    </row>
-    <row r="22" spans="1:2">
+      <c r="C21" s="18"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="18"/>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22"/>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:5">
       <c r="A23"/>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:5">
       <c r="A24"/>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:5">
       <c r="A25"/>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:5">
       <c r="A26"/>
     </row>
   </sheetData>
@@ -1983,27 +2024,37 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:11">
-      <c r="D3" s="18"/>
+      <c r="C3" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="D3" s="19">
+        <v>6938.23</v>
+      </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="D4" s="18"/>
+      <c r="C4" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="19">
+        <v>5656.84</v>
+      </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="14"/>
       <c r="C5" s="19" t="s">
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="D5" s="19">
-        <v>6850.67</v>
+        <v>4137.97</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="15"/>
       <c r="C6" s="19" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="D6" s="19">
-        <v>6123.55</v>
+        <v>4045.36</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2011,92 +2062,88 @@
         <v>86</v>
       </c>
       <c r="D7" s="19">
-        <v>5267.37</v>
+        <v>3994.25</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="15"/>
       <c r="C8" s="19" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="D8" s="19">
-        <v>4306.4799999999996</v>
+        <v>3089.22</v>
       </c>
       <c r="K8" s="17"/>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="15"/>
       <c r="C9" s="19" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D9" s="19">
-        <v>4267.5200000000004</v>
+        <v>2589.4899999999998</v>
       </c>
       <c r="K9" s="17"/>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="15"/>
       <c r="C10" s="19" t="s">
-        <v>73</v>
+        <v>3</v>
       </c>
       <c r="D10" s="19">
-        <v>4185.6099999999997</v>
+        <v>2244.14</v>
       </c>
       <c r="K10" s="17"/>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="15"/>
       <c r="C11" s="19" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="D11" s="19">
-        <v>3712.89</v>
+        <v>2150</v>
       </c>
       <c r="K11" s="17"/>
     </row>
     <row r="12" spans="1:11">
       <c r="C12" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="19">
+        <v>1542.97</v>
+      </c>
+      <c r="K12" s="17"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="C13" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" s="21">
+        <v>926.33</v>
+      </c>
+      <c r="K13" s="17"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="C14" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="19">
-        <v>3305.06</v>
-      </c>
-      <c r="K12" s="17"/>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="C13" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="19">
-        <v>2962.01</v>
-      </c>
-      <c r="K13" s="17"/>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="C14" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" s="19">
-        <v>992.53</v>
+      <c r="D14" s="21">
+        <v>34.270000000000003</v>
       </c>
       <c r="K14" s="17"/>
     </row>
     <row r="15" spans="1:11">
       <c r="C15" s="19" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D15" s="19">
-        <v>970.3</v>
+        <v>12.06</v>
       </c>
       <c r="K15" s="17"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="C16" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="D16" s="19">
-        <v>560.46</v>
-      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
       <c r="K16" s="17"/>
     </row>
     <row r="17" spans="11:11">
